--- a/jobs_input.xlsx
+++ b/jobs_input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://realpython.github.io/fake-jobs/</t>
+          <t>https://www.naukri.com/dot-net-developer-jobs-in-pune</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Pune, India</t>
         </is>
       </c>
     </row>
@@ -485,29 +485,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/jobs?q=.net+developer&amp;l=Pune</t>
+          <t>https://in.indeed.com/jobs?q=.net+developer&amp;l=Pune</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Software Engineer (.NET)</t>
+          <t>.NET Developer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3+ years</t>
+          <t>3-5 years</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Pune, India</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://remoteok.com</t>
+          <t>https://www.foundit.in/srp/results?query=.net%20developer&amp;locations=Pune</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -517,19 +517,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 years</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Pune, India</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://weworkremotely.com</t>
+          <t>https://www.shine.com/job-search/net-developer-jobs-in-pune</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Pune, India</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://upwork.com</t>
+          <t>https://www.timesjobs.com/candidate/job-search.html?searchType=personalizedSearch&amp;from=submit&amp;txtKeywords=.NET+Developer&amp;txtLocation=Pune</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,10 +561,2364 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3-5 years</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.co.in/Job/pune-net-developer-jobs-SRCH_IL.0,4_IC2856202_KO5,18.htm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.placementindia.com/job-search/dot-net-developer-jobs-in-pune.htm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.freshersworld.com/jobs/jobsearch/dot-net-developer-jobs-in-pune</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.apna.co/jobs</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.quikr.com/jobs</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://cutshort.io/jobs</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.cutshort.io/jobs/dot-net-developer-jobs-in-pune</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.instahyre.com/search-jobs/</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.hirist.tech/</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.hirist.tech/search/dot-net-developer-jobs-in-pune</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.techgig.com/jobs</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.turing.com/jobs</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.flexiple.com/jobs</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.uplers.com/jobs/</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.avasarai.com/remote-jobs/dot-net</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://wellfound.com/jobs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.ycombinator.com/jobs</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.ventureloop.com/</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://startup.jobs/</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://www.builtin.com/jobs</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://www.builtinpune.com/jobs</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://remoteok.com</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://remote.co/remote-jobs</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://remotive.com/remote-jobs/software-dev</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://remote.com/jobs</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.flexjobs.com/</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/jobs</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://jobgether.com/</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://remotefront.io/</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://nodesk.co/remote-jobs/</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.virtualvocations.com/</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://dailyremote.com/</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://justremote.co/</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://remotewoman.com/</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://www.dice.com/jobs</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://www.hackerrank.com/jobs</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://angel.co/jobs</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://stackoverflow.com/jobs</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://www.codementor.io/jobs</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.gun.io/</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://otta.com/</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.upwork.com/</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://www.toptal.com/talent/apply</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://www.freelancer.com/jobs/</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.guru.com/d/freelancers/q/.net/</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.peopleperhour.com/</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://www.remotelyawesome.com/</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://remoteleaf.com/</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://remoteok.com/remote-dev-jobs</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://weworkremotely.com/categories/remote-programming-jobs</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://remote.co/remote-jobs/developer/</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.workingnomads.com/remote-software-development-jobs</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=.NET+Developer+jobs+Pune</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=.NET+Developer+remote+India+jobs</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=C%23+Developer+jobs+Pune</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=.NET+Core+Developer+jobs+Pune</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?q=ASP.NET+Core+Developer+jobs+Pune</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.greenhouse.io/</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://jobs.lever.co/</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.workday.com/</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://www.smartrecruiters.com/</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://www.ashbyhq.com/</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://www.icims.com/</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://jobs.jobvite.com/</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://www.successfactors.com/</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://careers.oracle.com/</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.tcs.com/careers</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://www.infosys.com/careers</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.wipro.com/careers/</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://careers.hcltech.com/</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://www.techmahindra.com/en-in/careers/</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://www.cognizant.com/us/en/careers</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://careers.capgemini.com/</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/in-en/careers</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://www.ibm.com/careers</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com/in/en/careers.html</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://www.persistent.com/careers/</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.ltimindtree.com/careers/</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://www.nagarro.com/en/careers</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://www.epam.com/careers</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.globant.com/careers</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://www.publicissapient.com/careers</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://www.virtusa.com/careers</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://www.zoho.com/careers/</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://careers.freshworks.com/</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/in/careers/</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.cybage.com/careers</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.zensar.com/careers</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.qlik.com/us/company/careers</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.eaton.com/in/en-us/company/careers.html</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.mastercard.com/global/en/careers.html</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.fisglobal.com/en/careers</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.fiserv.com/en/careers.html</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://www.avalara.com/in/en/careers.html</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://www.bentley.com/en/careers/</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://www.vodafoneidea.com/careers</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>3-5 years</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Pune, India</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://remote.com/careers</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://about.gitlab.com/jobs/</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://automattic.com/work-with-us/</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://zapier.com/jobs</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://www.shopify.com/careers</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://www.atlassian.com/company/careers</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://www.github.careers/</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://careers.microsoft.com/</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://www.google.com/about/careers/applications/</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://www.amazon.jobs/</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>.NET Developer</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
         <is>
           <t>Remote</t>
         </is>
